--- a/www/download/COUNTRY.WEU.EXI382.xlsx
+++ b/www/download/COUNTRY.WEU.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - Europa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1422</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>211.852</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>149.957</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>149.48</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>149.337</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>148.994</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>148.838</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>147.9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>149.251</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>150.6</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>151.951</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>153.3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>154.651</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>158.7</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>159.3</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>159.9</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>161.1</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>163.9</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>163.562</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>167.823</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>143.396</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>133.292</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>132.866</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>147.461</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>159.184</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>178.044</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>183.386</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>163.358</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>53.457</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>101.195</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>103.744</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>104.887</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>106.722</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>107.764</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>110.058</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>112.738</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>115.426</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>117.204</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>118.622</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>120.783</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>124.526</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>124.131</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>126.008</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>127.798</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>130.975</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>129.348</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>131.528</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>111.395</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>102.937</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>102.358</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>113.834</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>122.943</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>137.437</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>141.382</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>427006.306</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>305893</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>303726</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>304849</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>306658</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>312324</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>302461</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>304765</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>308923</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>301733</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>308793</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>313414</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>317715</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>320003</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>325966</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>325974</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>324073</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>330235</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>330203</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>339406.914</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>290310.518</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>270089.018</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>268713.868</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>297917.148</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>321085.569</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>358533.548</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>369521.988</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327458.67</t>
+          <t>860418689445.036</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>99575</t>
+          <t>571979256733.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>567979422136.642</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>559769455228.06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>116022</t>
+          <t>562263815402.385</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>547884888804.595</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>515722610207.345</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>137401</t>
+          <t>504707883193.175</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>147361</t>
+          <t>542454166613.031</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>548361854462.972</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>158489</t>
+          <t>531753709695.97</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>162436</t>
+          <t>538501637125.594</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>565837980189.135</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>177955</t>
+          <t>525348194512.716</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>510687323553.601</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>183800</t>
+          <t>558350171580.815</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>186371</t>
+          <t>513167835210.138</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>508149866282.197</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>188961</t>
+          <t>504833247009.381</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>264467.175</t>
+          <t>525537600057.897</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>224133.017</t>
+          <t>453971558275.509</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>207310.455</t>
+          <t>432430555771.691</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>205701.244</t>
+          <t>412676020955.875</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>228525.701</t>
+          <t>469204306404.065</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>246426.094</t>
+          <t>507189279928.433</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>275030.458</t>
+          <t>562860294937.645</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>283157.683</t>
+          <t>557636829198.3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>112770300801.487</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>92130272930.568</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>83262202427.5448</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>82935194009.2793</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>92960729676.1899</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>80866758639.1042</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>89844207777.2374</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>88228997520.0766</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>80851184033.3211</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>85086249377.3769</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>78048364117.8518</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>84654065359.7788</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>100908336152.254</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>92923703957.3246</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>68647731303.0805</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>77571439097.4328</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>78395803145.7829</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>79363386306.6553</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>75759993245.4818</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>74771946451.8806</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>66683630890.2668</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>60688599187.4361</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>63232475545.6956</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>60939937211.8653</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>64676949777.0196</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>74193610095.6481</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>86153901829.6391</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>195099566760.114</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>328771456.247104</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>290597927.706675</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>304170982.148922</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>371753371.859676</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>329443412.325867</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>279709783.562437</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>254274470.183517</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>250699607.570325</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>241806942.58987</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2570656047.79548</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>160037970.162459</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>148802753.802091</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>115301157.104113</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>144395250.777062</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>141938852.783892</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>114513726.407719</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>108757858.650422</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>98027487.1211027</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>23775617545.08</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>24825243936.5357</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2981766589089.27</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>20689489437.4865</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>23157360589.3219</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>23475121357.1311</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>26464147441.2082</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>27460886830.7074</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1153359.50556486</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1744350.20975149</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1893391.76858763</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2006974.27610458</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2101510.78978582</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2448931.72858054</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2262418.50709583</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2348924.61003724</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2299803.17949063</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2159989.90191853</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2296088.25545141</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2573747.57690434</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2710744.67544488</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2579725.18798996</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2573235.06905901</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3289807.01831899</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3119081.06647521</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3440516.68173086</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3385609.40142728</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3578434.09817533</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>3491691.22537431</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2978342.75109835</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3120356.94214853</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3391602.18160386</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>3845468.97025815</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>4076274.22653772</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4113939.66105375</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3207298.97960269</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4346511.80016576</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4700952.12746885</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4763045.27982619</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5046483.52475292</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5878154.77474342</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5555751.51343545</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5270481.06868934</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5203644.32188804</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5140575.31645138</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5344003.42380184</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5789059.48151095</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6302253.71408847</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5879439.32476181</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5727434.4782304</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>7221343.62769774</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>6909451.21006184</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>7551792.56588634</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7328653.77095537</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>7896853.49679931</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>7705780.02704573</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6690322.43365529</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>6750179.08341689</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7464315.45164459</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>8596792.73365645</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>9075816.63358758</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>8827759.13639428</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.90376692676583</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0808065235510995</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.181280306457841</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.317667382411684</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.248075401346144</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.571473892842623</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.448540793221015</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.55732246610366</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.822620184995855</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.767112795549296</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.03065114549567</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.918821019519661</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.683498177431864</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.915065719741213</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.59597799690141</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.36942877608704</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.37730838286667</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.4464051880266</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.49420560780373</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.5369839522863</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2.36113996845084</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.41597034408014</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2.2530949029299</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2.75001536274791</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2.81010692376116</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2.70692917395135</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2.28664955757081</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>690.324293148538</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1723.44637616273</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>822.789687509563</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>799.421595555097</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>886.294103904182</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>757.732788357504</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>833.71262923829</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>801.659102655257</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>717.159999585722</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>737.149770219817</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>665.918945751547</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>713.645574680581</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>835.451480359157</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>746.219295225887</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>553.026490587246</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>615.607255868146</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>613.435289643027</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>605.943014366519</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>585.706723300532</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>568.487867868178</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>598.62542128498</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>589.571427580687</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>617.758630537026</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>535.342259022548</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>526.074555165726</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>539.836054079583</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>609.36757692757</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-128515168667.059</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-79627844856.0921</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-77718368604.5369</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-75420139667.2755</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-84039192504.9803</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-99209592006.7386</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>-85687105233.2221</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>-79759847403.6955</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-81052231756.6541</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-85187592935.1344</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-69837064741.2007</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-69481620212.7566</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>-63279449059.664</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>-64624991468.761</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>-68751783520.3066</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>-92039545577.9749</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>-91500200146.5983</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>-102679655079.156</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>-95031791746.7332</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-104511339003.152</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>-89740887260.5598</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>-89319038874.7432</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>-82536363489.9362</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>-95000394923.8773</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-101862433758.509</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>-114897988684.885</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>-111416876372.089</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-111592038140.662</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-73421077736.3477</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-72167491627.0043</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-70336183742.768</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-79501544035.8895</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-94793051618.0448</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-82176552742.4687</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-75683636231.8405</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-75815507144.2709</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-79711522323.608</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-64489731465.4343</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-63457917549.4567</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-57482841069.2839</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-58939947189.2334</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-63474811842.7885</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-85856541254.0326</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-86559037504.2641</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-97323515194.2079</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-89315107627.36</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-99531298031.5879</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-85156289412.6562</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-83570611595.358</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-82210085255.7151</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-94613021491.0505</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-101487815540.293</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-114420896681.238</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-108947275256.964</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-16923130526.3974</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-6206767119.74442</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-5550876977.53254</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-5083955924.50752</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-4537648469.09083</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-4416540388.69387</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-3510552490.75339</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-4076211171.85497</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-5236724612.38322</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-5476070611.5264</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-5347333275.76635</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-6023702663.29992</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-5796607990.38015</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-5685044279.52755</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-5276971677.5181</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-6183004323.94231</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-4941162642.33423</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-5356139884.94855</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-5716684119.37318</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-4980040971.56428</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-4584597847.90362</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-5748427279.38517</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-326278234.221091</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-387373432.826831</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-374618218.216274</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-477092003.646253</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-2469601115.12513</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>2004.54085118773</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1862.71208634718</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>971.945254211647</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>1053.37176125846</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>1106.16186944093</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1190.75729465466</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1207.66675327521</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1248.44173072153</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1307.11029111656</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>1302.62679119166</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1352.24906999765</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>1369.35812918429</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>1406.48104451739</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1429.05899169654</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>1435.6446012681</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>1458.63754682197</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>1458.32485641461</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>1482.38213399473</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>1460.87299378453</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>2010.7324657192</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>2012.06382961167</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>2013.95851233262</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>2009.62745224095</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>2007.54169566272</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2004.4003050515</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>2001.13401801838</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>2002.777677107</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2015.58444270668</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>2039.87142980929</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2031.88386406168</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>2041.34943115193</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>2058.19026269493</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2098.41572716658</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2045.03718728835</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2041.96286791913</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>2051.28154050357</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1985.72566156252</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2014.30528375716</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>2026.58890016871</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>2036.63461538428</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2016.40201638264</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>2046.23979912131</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>2038.61163226988</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>2011.62631905719</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>2014.85661988968</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>2018.82466587631</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2022.40854306836</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>2024.54199111824</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>2026.29207123187</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>2022.44512855012</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>2020.31766818866</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2017.06980123866</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>2013.73943603966</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>2014.99431602254</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>35513.9365785421</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>36423.7168435444</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>38510.9626871245</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>36396.2387563615</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>35605.798511954</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>45078.1454743491</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>51380.3473407069</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>52662.2809649012</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>53836.2272874849</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>62269.4652456233</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>64139.0356991252</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>71678.5140300508</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>74800.5696438885</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>98040.0311292388</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>77707.8053220371</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>107803.968201147</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>135865.793594475</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>152597.840231206</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>144364.550686392</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>137514.850004703</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>138762.949182524</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>139552.563397428</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>159976.384846049</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>170071.91971604</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>184655.042854321</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>194866.150709162</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>207636.165530384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>126824527398.551</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>79309684679.7657</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>78573109611.1752</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>77787109992.1715</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>86909556527.6221</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>103325544076.34</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>93384358109.8526</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>86908693797.0272</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>87928805463.6653</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>93621751285.151</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>77226469350.2145</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>76595113442.7107</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>65941228655.0582</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>72514698311.0287</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>75574907402.4958</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>95952220770.1579</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>99043813854.4342</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>110321903486.403</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>101686802589.788</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>109434005736.476</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>96851878207.2212</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>96651251814.5901</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>93728485854.0922</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>105253200785.192</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>112633432818.242</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>126687164181.796</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>122102557699.372</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>48592.6740311106</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>49960.4167169811</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>55648.6460508899</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>51061.3145113142</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>43578.2994067773</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>54317.7259100221</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>61992.4749595004</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>67576.0096310371</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>71751.3423584277</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>83372.9542918093</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>92085.5840721939</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>115662.501772917</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>133142.69980503</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>167170.484827745</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>119866.959566201</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>165478.290546245</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>197246.830774359</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>220763.440631861</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>214307.788521144</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>183883.803016814</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>166511.81955051</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>181640.436458987</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>207225.243048427</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>229041.247237232</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>250131.541153699</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>262279.949261223</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>274145.518270653</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>427006.306</t>
+          <t>5718806680.49732</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>305893</t>
+          <t>2431658623.38352</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>303726</t>
+          <t>4062704833.36878</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>304849</t>
+          <t>5129845967.52304</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>306658</t>
+          <t>4332870622.5883</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>312324</t>
+          <t>5549385922.38966</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>9408766085.43944</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>304765</t>
+          <t>9644413565.92937</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>308923</t>
+          <t>9919951481.82341</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>301733</t>
+          <t>12304323864.4524</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>308793</t>
+          <t>12063481154.045</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>313414</t>
+          <t>13657945521.1412</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>317715</t>
+          <t>9906845574.33874</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>320003</t>
+          <t>17363299244.0978</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>325966</t>
+          <t>13028589239.1356</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>325974</t>
+          <t>11024035430.9577</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>324073</t>
+          <t>14621814371.7601</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>330235</t>
+          <t>15074427767.9311</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>330203</t>
+          <t>14667257511.6983</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>339406.914</t>
+          <t>9851968943.28429</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>290310.518</t>
+          <t>9793332265.32601</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>270089.018</t>
+          <t>11795906785.112</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>268713.868</t>
+          <t>15743262652.4008</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>297917.148</t>
+          <t>16113749995.798</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>321085.569</t>
+          <t>16746869219.8687</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>358533.548</t>
+          <t>18331099927.897</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>369521.988</t>
+          <t>17166025032.2866</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>327458.67</t>
+          <t>-13078.7374525685</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>99575</t>
+          <t>-13536.6998734367</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>-17137.6833637655</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>-14665.0757549527</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>116022</t>
+          <t>-7972.50089482337</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>-9239.58043567293</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>-10612.1276187935</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>137401</t>
+          <t>-14913.7286661359</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>147361</t>
+          <t>-17915.1150709428</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>-21103.489046186</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>158489</t>
+          <t>-27946.5483730687</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>162436</t>
+          <t>-43983.9877428665</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>-58342.1301611416</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>177955</t>
+          <t>-69130.4536985063</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>-42159.1542441634</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>183800</t>
+          <t>-57674.3223450978</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>186371</t>
+          <t>-61381.0371798844</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>-68165.6004006547</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>188961</t>
+          <t>-69943.2378347521</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>264467.175</t>
+          <t>-46368.9530121113</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>224133.017</t>
+          <t>-27748.8703679858</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>207310.455</t>
+          <t>-42087.8730615591</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>205701.244</t>
+          <t>-47248.8582023776</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>228525.701</t>
+          <t>-58969.3275211923</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>246426.094</t>
+          <t>-65476.4982993779</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>275030.458</t>
+          <t>-67413.7985520604</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>283157.683</t>
+          <t>-66509.3527402682</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>636727.07</t>
+          <t>121105720718.053</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>431633.969</t>
+          <t>76878026056.3821</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>428029.173</t>
+          <t>74510404777.8064</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>426666.609</t>
+          <t>72657264024.6485</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>430073.596</t>
+          <t>82576685905.0338</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>418575.081</t>
+          <t>97776158153.9508</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>393353.772</t>
+          <t>83975592024.4132</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>391597.916</t>
+          <t>77264280231.0979</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>420734.305</t>
+          <t>78008853981.8419</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>421003.473</t>
+          <t>81317427420.6986</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>409765.692</t>
+          <t>65162988196.1695</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>417698.691</t>
+          <t>62937167921.5695</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>436346.587</t>
+          <t>56034383080.7194</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>406656.23</t>
+          <t>55151399066.9309</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>396651.268</t>
+          <t>62546318163.3602</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>434844.094</t>
+          <t>84928185339.2003</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>399854.078</t>
+          <t>84421999482.6741</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>396447.568</t>
+          <t>95247475718.4719</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>394541.306</t>
+          <t>87019545078.0896</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>408867.327</t>
+          <t>99582036793.1916</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>353286.801</t>
+          <t>87058545941.8952</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>335526.393</t>
+          <t>84855345029.4781</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>323064.201</t>
+          <t>77985223201.6914</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>366074.55</t>
+          <t>89139450789.394</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>395002.399</t>
+          <t>95886563598.3729</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>438360.696</t>
+          <t>108356064253.899</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>437739.053</t>
+          <t>104936532667.085</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>59902.4838166813</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>61221.4541268133</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>69654.8792770103</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>64237.4834215236</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>52774.0605447431</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.898</t>
+          <t>53793.5222756187</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.682</t>
+          <t>69211.5153737556</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3.559</t>
+          <t>79230.5594193136</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>75486.4349901508</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3.453</t>
+          <t>81630.4213860439</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3.593</t>
+          <t>100205.853687756</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.927</t>
+          <t>124667.564856346</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4.233</t>
+          <t>139697.638910135</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>156135.60612956</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.884</t>
+          <t>123265.925056283</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>4.901</t>
+          <t>136999.874009792</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>4.697</t>
+          <t>149093.615981621</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>167195.094256258</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>4.973</t>
+          <t>171274.559535439</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>5.294</t>
+          <t>153492.897682306</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>5.107</t>
+          <t>143727.570129142</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>4.402</t>
+          <t>143647.513990027</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>156897.511133313</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.897</t>
+          <t>164920.686472636</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>182920.777566253</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>5.909</t>
+          <t>197428.168798318</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>203128.857357142</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>309410.529</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>229547.78</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>228763.777</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>235866.516</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>234143.928</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>228257.462</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>210013.06</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>224935.969</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>239743.099</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>230413.134</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>228471.681</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>239411.477</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>243379.966</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>230507.349</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>229442.787</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>254366.003</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>231655.457</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>231507.695</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>233217.21</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>238145.695</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>205706.431</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>192505.881</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>190764.789</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>213194.949</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>226873.056</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>252800.713</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>259871.643</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>70287.8944766489</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>71609.2807042965</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>79724.0218405472</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>71943.224384307</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>62946.8565664394</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.125</t>
+          <t>63487.6882197162</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.966</t>
+          <t>83227.9982188595</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>88102.9116143009</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.006</t>
+          <t>84803.8375672419</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>92803.5356582779</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>109733.324824004</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>138134.491117405</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>169626.50620534</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.267</t>
+          <t>192463.340572459</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.246</t>
+          <t>131071.078080303</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.867</t>
+          <t>167742.659362229</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2.721</t>
+          <t>187350.095174757</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>206780.445067277</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.939</t>
+          <t>215851.985236815</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3.083</t>
+          <t>194069.11057918</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>176625.686810681</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>179370.850172061</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>200244.904447387</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.852</t>
+          <t>191543.650779169</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>217250.6782322</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>226719.70804668</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3.437</t>
+          <t>259284.948247947</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>93887.366</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>79176.363</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>72774.949</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>72471.044</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>81081.161</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>72005.422</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80094.749</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>78682.551</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>71817.353</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>75894.482</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>69356.995</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>75612.216</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>89119.845</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>82370.4</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>61193.776</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>69288.078</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>69657.848</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>71310.554</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>68033.47</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>67292.032</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>60201.99</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>54600.603</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>57328.518</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>55281.998</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>58655.972</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>67266.005</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>77876.593</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>248.78</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>43.09</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>76.49</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>62.49</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>74.63</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>105.19</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>98.11</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>128.51</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>114.83</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>90.62</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>116.04</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>191.22</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>165.27</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>167.55</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>172.27</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>177.75</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>293.01</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>272.3</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>279.69</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>258.81</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>313.38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>320.12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>308.87</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>263.6</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>222739.445</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>313.455</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>278.279</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>295.521</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>362.413</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>319.235</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>273.165</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>251.241</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>247.347</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>238.069</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2905.603</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>157.92</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>145.749</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>113.692</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>143.008</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>141.52</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>114.014</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>108.195</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>97.43</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>27136.753</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>28337.779</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3405755.888</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>23617.742</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>26436.225</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>26799.233</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>30211.663</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>31351.978</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>17335.2148927881</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>17920.6577332149</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24148.9858736149</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>23713.4273280041</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>18800.511646813</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>23743.9769595746</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>24860.5686702467</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>27651.4325726593</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>32259.0761305595</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>37079.6079447135</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>47607.7258511527</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>48110.6031756221</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>56693.0983816981</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>65776.623769874</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>66678.8670047517</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>61434.4588848228</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>65665.0561988276</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>72411.775338853</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>76962.1657061766</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>68515.2477905218</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>63992.8969459832</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>64031.2885494258</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>73683.3155983215</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>85155.4040625517</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>98405.1250026854</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>102742.079363347</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>89710.9985163439</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>327458669788.794</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>99574999999.9012</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>98355999999.9649</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>109281000000.012</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>116022000000.041</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>127080000000.158</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130142999999.953</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>137400999999.819</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>147360999999.946</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>150357000000.061</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>158488999999.979</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>162436000000.135</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>169879000000.001</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>177955000000.053</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>178207999999.997</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>183799999999.941</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>186371000000.035</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>194154999999.961</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>188961000000.053</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>264467174681.512</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>224133017026.699</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>207310455048.048</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>205701243897.342</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>228525700749.388</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>246426094153.175</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>275030457784.329</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>283157683331.383</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>427006305889.841</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>305892999999.924</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>303725999999.956</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>304848999999.953</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>306657999999.961</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>312324000000.077</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>302460999999.982</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>304764999999.889</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>308922999999.931</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>301733000000.058</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>308792999999.987</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>313414000000.036</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>317715000000.013</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>320002999999.994</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>325966000000.015</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>325973999999.976</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>324073000000.062</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>330234999999.905</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>330203000000.062</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>339406914217.666</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>290310518367.437</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>270089017662.905</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>268713868433.452</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>297917147937.803</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>321085569008.149</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>358533547517.478</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>369521988326.851</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>309410529092.62</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>229547780456.806</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>228763776664.902</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>235866516312.603</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>234143927940.815</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>228257461604.855</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>210013060346.425</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>224935969271.409</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>239743099246.25</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>230413133807.557</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>228471681396.683</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>239411477483.952</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>243379965572.21</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>230507348573.481</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>229442787217.714</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>254366002761.705</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>231655457150.798</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>231507695227.327</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>233217210233.307</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>238145695457.392</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>205706430891.696</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>192505880532.335</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>190764788746.327</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>213194948622.828</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>226873055852.169</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>252800712709.948</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>259871642696.423</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>211852352.51986</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>149957000.000006</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>149480000.000008</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>149337000.000009</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>148993999.999996</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>148838000.000028</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>147900000.000017</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>149251000.000044</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150600000.000045</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>151950999.999985</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>153300000.000007</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154651000.000022</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>156000000.000032</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>158700000.000034</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>159299999.999995</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>159900000.000011</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>161099999.999974</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>163899999.999993</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>163562000.000001</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>167823121.288206</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>143395651.777559</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>133292244.241328</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>132865838.800824</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>147460546.739119</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>159184163.488529</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>178043663.991897</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>183386119.448844</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>163358441.707371</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>53457000.0000214</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>101195000.000018</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>103744000.000014</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>104886999.999991</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>106722000.000019</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>107764000.000003</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>110058000.000055</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>112738000.000036</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>115425999.999979</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>117203999.999981</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>118622000.000026</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>120783000.000041</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>124526000.000035</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>124130999.999991</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>126007999.999999</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>127797999.999973</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>130975000.000001</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>129348000.000008</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>131527778.652998</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>111394585.861601</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>102936805.19165</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>102357899.056346</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>113833601.186524</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>122942554.704332</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>137437300.704466</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>141382484.220816</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>427006305889.841</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>305892999999.924</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>303725999999.956</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>304848999999.953</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>306657999999.961</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>312324000000.077</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>302460999999.982</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>304764999999.889</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>308922999999.931</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>301733000000.058</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>308792999999.987</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>313414000000.036</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>317715000000.013</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>320002999999.994</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>325966000000.015</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>325973999999.976</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>324073000000.062</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>330234999999.905</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>330203000000.062</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>339406914217.666</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>290310518367.437</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>270089017662.905</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>268713868433.452</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>297917147937.803</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>321085569008.149</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>358533547517.478</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>369521988326.851</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>327458669788.794</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>99574999999.9012</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>98355999999.9649</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>109281000000.012</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>116022000000.041</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>127080000000.158</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>130142999999.953</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>137400999999.819</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>147360999999.946</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>150357000000.061</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>158488999999.979</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>162436000000.135</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>169879000000.001</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>177955000000.053</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>178207999999.997</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>183799999999.941</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>186371000000.035</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>194154999999.961</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>188961000000.053</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>264467174681.512</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>224133017026.699</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>207310455048.048</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>205701243897.342</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>228525700749.388</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>246426094153.175</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>275030457784.329</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>283157683331.383</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>245921.134091221</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>243890.37287545</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>284967.500432286</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>260932.334636838</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>222023.675857919</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>249724.36213619</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>296800.995985054</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>318197.893535867</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>326357.943638747</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>384018.428536622</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>457140.906111636</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>541910.221677108</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>634064.740381153</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>731118.242250106</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>565544.949221538</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>653241.272725927</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>725564.682266605</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>782782.040552982</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>809413.32470182</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>700765.943628349</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>655652.074183665</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>656917.048829123</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>735775.954134435</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>804085.506261315</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>902660.524372509</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>918389.738838523</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>965379.129212184</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>87217.4011704634</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>88212.9925310794</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>97957.4744710881</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>91033.6499575653</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>78733.2848592136</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>84204.1781212518</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>103803.497577904</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>113034.688197105</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>111821.340167651</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>124829.416916465</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>148833.793988687</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>183386.924703425</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>216146.335385941</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>244997.862868774</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>182141.163346158</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>215762.763039563</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>238064.816793387</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>264065.13784472</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>274371.732712263</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>245609.188571119</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>225755.951279672</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>227462.369317126</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>253114.36025543</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>265800.991599897</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>297887.998269403</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>303264.244306462</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>326512.587927545</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
